--- a/public/sample_excel.xlsx
+++ b/public/sample_excel.xlsx
@@ -1,174 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63ACB7B3-7C13-4DD4-87EE-C01917637A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DMA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
-  <si>
-    <t>Manpower supply for  DMA - Feb'26</t>
-  </si>
-  <si>
-    <t>Sl No.</t>
-  </si>
-  <si>
-    <t>EMP Code</t>
-  </si>
-  <si>
-    <t>Resource Name</t>
-  </si>
-  <si>
-    <t>Date of Joining</t>
-  </si>
-  <si>
-    <t>Bank Account No</t>
-  </si>
-  <si>
-    <t>Designation</t>
-  </si>
-  <si>
-    <t>Category(Internal / T&amp;M)</t>
-  </si>
-  <si>
-    <t>Project Name</t>
-  </si>
-  <si>
-    <t>CTC (Per Month)</t>
-  </si>
-  <si>
-    <t>Gross Amount (Per Month)</t>
-  </si>
-  <si>
-    <t>Billyable Days</t>
-  </si>
-  <si>
-    <t>Base Components (A)</t>
-  </si>
-  <si>
-    <t>Employer's Share of (B)</t>
-  </si>
-  <si>
-    <t>Employee's  Share of</t>
-  </si>
-  <si>
-    <t>Net Credited Amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salary Credited Date </t>
-  </si>
-  <si>
-    <t>Salary Paid</t>
-  </si>
-  <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>HRA</t>
-  </si>
-  <si>
-    <t>other allowance</t>
-  </si>
-  <si>
-    <t>Provident Fund</t>
-  </si>
-  <si>
-    <t>ESIC</t>
-  </si>
-  <si>
-    <t>Professional Tax</t>
-  </si>
-  <si>
-    <t>LWF</t>
-  </si>
-  <si>
-    <t>Gratuity</t>
-  </si>
-  <si>
-    <t>VPF</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>Other recovery</t>
-  </si>
-  <si>
-    <t>Salary Advance</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -180,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -229,47 +118,176 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -589,194 +607,418 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:30" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Manpower supply for  DMA - Feb'26</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="8" t="n"/>
+      <c r="M1" s="8" t="n"/>
+      <c r="N1" s="8" t="n"/>
+      <c r="O1" s="8" t="n"/>
+      <c r="P1" s="8" t="n"/>
+      <c r="Q1" s="8" t="n"/>
+      <c r="R1" s="8" t="n"/>
+      <c r="S1" s="8" t="n"/>
+      <c r="T1" s="8" t="n"/>
+      <c r="U1" s="8" t="n"/>
+      <c r="V1" s="8" t="n"/>
+      <c r="W1" s="8" t="n"/>
+      <c r="X1" s="8" t="n"/>
+      <c r="Y1" s="8" t="n"/>
+      <c r="Z1" s="8" t="n"/>
+      <c r="AA1" s="8" t="n"/>
+      <c r="AB1" s="8" t="n"/>
+      <c r="AC1" s="8" t="n"/>
+      <c r="AD1" s="9" t="n"/>
     </row>
-    <row r="2" spans="1:30">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>17</v>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Sl No.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>EMP Code</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Resource Name</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Date of Joining</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Bank Account No</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Designation</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Category(Internal / T&amp;M)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>CTC (Per Month)</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Gross Amount (Per Month)</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Billyable Days</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Base Components (A)</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n"/>
+      <c r="N2" s="9" t="n"/>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>Employer's Share of (B)</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="n"/>
+      <c r="Q2" s="8" t="n"/>
+      <c r="R2" s="8" t="n"/>
+      <c r="S2" s="9" t="n"/>
+      <c r="T2" s="6" t="inlineStr">
+        <is>
+          <t>Employee's  Share of</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n"/>
+      <c r="V2" s="8" t="n"/>
+      <c r="W2" s="8" t="n"/>
+      <c r="X2" s="8" t="n"/>
+      <c r="Y2" s="8" t="n"/>
+      <c r="Z2" s="8" t="n"/>
+      <c r="AA2" s="9" t="n"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>Net Credited Amount</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salary Credited Date </t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>Salary Paid</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="45.75">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
+    <row r="3" ht="45.75" customHeight="1">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>HRA</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>other allowance</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>Provident Fund</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>ESIC</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>Professional Tax</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>LWF</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>Gratuity</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
+        <is>
+          <t>Provident Fund</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>VPF</t>
+        </is>
+      </c>
+      <c r="V3" s="7" t="inlineStr">
+        <is>
+          <t>ESIC</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>TDS</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>Other recovery</t>
+        </is>
+      </c>
+      <c r="Y3" s="7" t="inlineStr">
+        <is>
+          <t>Salary Advance</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>LWF</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>Professional Tax</t>
+        </is>
+      </c>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="11" t="n"/>
+      <c r="AD3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>John Doe</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1-Apr-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MahaIT Internal Project Delivery</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>120,513</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>115,072</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>36,154</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>18,077</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>60,841</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1,739</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>6,576</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>106,496</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>30-Jan-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>30-Jan-26</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:S2"/>
     <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="L2:N2"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="I2:I3"/>
+    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
